--- a/HMA_開發人天評估表_含維護.xlsx
+++ b/HMA_開發人天評估表_含維護.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects_in\git-okProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4AD29AC-E582-4443-A37F-7C28D7A48F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3FC4F8-7990-4484-9926-53DECFB1DC47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="0" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="開發人天評估" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="519">
   <si>
     <t>序號</t>
   </si>
@@ -1534,18 +1534,9 @@
     <t>A7</t>
   </si>
   <si>
-    <t>保固1年</t>
-  </si>
-  <si>
     <t>維護</t>
   </si>
   <si>
-    <t>A8</t>
-  </si>
-  <si>
-    <t>小修改維護1年</t>
-  </si>
-  <si>
     <t>其他工作項目 小計</t>
   </si>
   <si>
@@ -1588,20 +1579,23 @@
     <t>其他工作項目費用</t>
   </si>
   <si>
-    <t>總開發費用 (NT$)</t>
-  </si>
-  <si>
     <t>預估工期 (以6人計算)</t>
   </si>
   <si>
     <t>200 天 (9.5月)</t>
+  </si>
+  <si>
+    <t>總開發費用 (含稅NT$)</t>
+  </si>
+  <si>
+    <t>保固+需求單處理 1年</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1644,8 +1638,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1682,6 +1683,11 @@
         <bgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1707,10 +1713,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1735,21 +1742,32 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2050,7 +2068,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H260"/>
+  <dimension ref="A1:H259"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2089,16 +2107,16 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
@@ -3669,16 +3687,16 @@
       <c r="H65" s="6"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="12" t="s">
+      <c r="A66" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="B66" s="13"/>
-      <c r="C66" s="13"/>
-      <c r="D66" s="13"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13"/>
-      <c r="H66" s="13"/>
+      <c r="B66" s="25"/>
+      <c r="C66" s="25"/>
+      <c r="D66" s="25"/>
+      <c r="E66" s="25"/>
+      <c r="F66" s="25"/>
+      <c r="G66" s="25"/>
+      <c r="H66" s="25"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
@@ -3724,16 +3742,16 @@
       <c r="H68" s="6"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="12" t="s">
+      <c r="A69" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="B69" s="13"/>
-      <c r="C69" s="13"/>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
-      <c r="H69" s="13"/>
+      <c r="B69" s="25"/>
+      <c r="C69" s="25"/>
+      <c r="D69" s="25"/>
+      <c r="E69" s="25"/>
+      <c r="F69" s="25"/>
+      <c r="G69" s="25"/>
+      <c r="H69" s="25"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
@@ -4629,16 +4647,16 @@
       <c r="H105" s="6"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" s="12" t="s">
+      <c r="A106" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="B106" s="13"/>
-      <c r="C106" s="13"/>
-      <c r="D106" s="13"/>
-      <c r="E106" s="13"/>
-      <c r="F106" s="13"/>
-      <c r="G106" s="13"/>
-      <c r="H106" s="13"/>
+      <c r="B106" s="25"/>
+      <c r="C106" s="25"/>
+      <c r="D106" s="25"/>
+      <c r="E106" s="25"/>
+      <c r="F106" s="25"/>
+      <c r="G106" s="25"/>
+      <c r="H106" s="25"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
@@ -4759,16 +4777,16 @@
       <c r="H111" s="6"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="12" t="s">
+      <c r="A112" s="26" t="s">
         <v>219</v>
       </c>
-      <c r="B112" s="13"/>
-      <c r="C112" s="13"/>
-      <c r="D112" s="13"/>
-      <c r="E112" s="13"/>
-      <c r="F112" s="13"/>
-      <c r="G112" s="13"/>
-      <c r="H112" s="13"/>
+      <c r="B112" s="25"/>
+      <c r="C112" s="25"/>
+      <c r="D112" s="25"/>
+      <c r="E112" s="25"/>
+      <c r="F112" s="25"/>
+      <c r="G112" s="25"/>
+      <c r="H112" s="25"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
@@ -4939,16 +4957,16 @@
       <c r="H119" s="6"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A120" s="12" t="s">
+      <c r="A120" s="26" t="s">
         <v>233</v>
       </c>
-      <c r="B120" s="13"/>
-      <c r="C120" s="13"/>
-      <c r="D120" s="13"/>
-      <c r="E120" s="13"/>
-      <c r="F120" s="13"/>
-      <c r="G120" s="13"/>
-      <c r="H120" s="13"/>
+      <c r="B120" s="25"/>
+      <c r="C120" s="25"/>
+      <c r="D120" s="25"/>
+      <c r="E120" s="25"/>
+      <c r="F120" s="25"/>
+      <c r="G120" s="25"/>
+      <c r="H120" s="25"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="3">
@@ -5394,16 +5412,16 @@
       <c r="H138" s="6"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A139" s="12" t="s">
+      <c r="A139" s="26" t="s">
         <v>269</v>
       </c>
-      <c r="B139" s="13"/>
-      <c r="C139" s="13"/>
-      <c r="D139" s="13"/>
-      <c r="E139" s="13"/>
-      <c r="F139" s="13"/>
-      <c r="G139" s="13"/>
-      <c r="H139" s="13"/>
+      <c r="B139" s="25"/>
+      <c r="C139" s="25"/>
+      <c r="D139" s="25"/>
+      <c r="E139" s="25"/>
+      <c r="F139" s="25"/>
+      <c r="G139" s="25"/>
+      <c r="H139" s="25"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="3">
@@ -6099,16 +6117,16 @@
       <c r="H167" s="6"/>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A168" s="12" t="s">
+      <c r="A168" s="26" t="s">
         <v>325</v>
       </c>
-      <c r="B168" s="13"/>
-      <c r="C168" s="13"/>
-      <c r="D168" s="13"/>
-      <c r="E168" s="13"/>
-      <c r="F168" s="13"/>
-      <c r="G168" s="13"/>
-      <c r="H168" s="13"/>
+      <c r="B168" s="25"/>
+      <c r="C168" s="25"/>
+      <c r="D168" s="25"/>
+      <c r="E168" s="25"/>
+      <c r="F168" s="25"/>
+      <c r="G168" s="25"/>
+      <c r="H168" s="25"/>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="3">
@@ -7454,16 +7472,16 @@
       <c r="H222" s="6"/>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A223" s="12" t="s">
+      <c r="A223" s="26" t="s">
         <v>433</v>
       </c>
-      <c r="B223" s="13"/>
-      <c r="C223" s="13"/>
-      <c r="D223" s="13"/>
-      <c r="E223" s="13"/>
-      <c r="F223" s="13"/>
-      <c r="G223" s="13"/>
-      <c r="H223" s="13"/>
+      <c r="B223" s="25"/>
+      <c r="C223" s="25"/>
+      <c r="D223" s="25"/>
+      <c r="E223" s="25"/>
+      <c r="F223" s="25"/>
+      <c r="G223" s="25"/>
+      <c r="H223" s="25"/>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" s="3">
@@ -8084,16 +8102,16 @@
       <c r="H248" s="6"/>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A250" s="14" t="s">
+      <c r="A250" s="24" t="s">
         <v>482</v>
       </c>
-      <c r="B250" s="13"/>
-      <c r="C250" s="13"/>
-      <c r="D250" s="13"/>
-      <c r="E250" s="13"/>
-      <c r="F250" s="13"/>
-      <c r="G250" s="13"/>
-      <c r="H250" s="13"/>
+      <c r="B250" s="25"/>
+      <c r="C250" s="25"/>
+      <c r="D250" s="25"/>
+      <c r="E250" s="25"/>
+      <c r="F250" s="25"/>
+      <c r="G250" s="25"/>
+      <c r="H250" s="25"/>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" s="3" t="s">
@@ -8115,7 +8133,7 @@
         <v>10</v>
       </c>
       <c r="G251" s="5">
-        <f t="shared" ref="G251:G258" si="9">F251*8000</f>
+        <f t="shared" ref="G251:G257" si="9">F251*8000</f>
         <v>80000</v>
       </c>
       <c r="H251" s="2"/>
@@ -8246,103 +8264,78 @@
       <c r="H256" s="2"/>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A257" s="3" t="s">
+      <c r="A257" s="18" t="s">
         <v>499</v>
       </c>
-      <c r="B257" s="2" t="s">
+      <c r="B257" s="19" t="s">
+        <v>518</v>
+      </c>
+      <c r="C257" s="19" t="s">
+        <v>485</v>
+      </c>
+      <c r="D257" s="19" t="s">
         <v>500</v>
       </c>
-      <c r="C257" s="2" t="s">
+      <c r="E257" s="19" t="s">
         <v>485</v>
       </c>
-      <c r="D257" s="2" t="s">
+      <c r="F257" s="20">
+        <v>120</v>
+      </c>
+      <c r="G257" s="21">
+        <f t="shared" si="9"/>
+        <v>960000</v>
+      </c>
+      <c r="H257" s="19"/>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A258" s="6"/>
+      <c r="B258" s="6" t="s">
         <v>501</v>
       </c>
-      <c r="E257" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="F257" s="4">
-        <v>30</v>
-      </c>
-      <c r="G257" s="5">
-        <f t="shared" si="9"/>
-        <v>240000</v>
-      </c>
-      <c r="H257" s="2"/>
-    </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A258" s="3" t="s">
+      <c r="C258" s="6"/>
+      <c r="D258" s="6"/>
+      <c r="E258" s="6"/>
+      <c r="F258" s="7">
+        <f>SUM(F251:F257)</f>
+        <v>174</v>
+      </c>
+      <c r="G258" s="8">
+        <f>SUM(G251:G257)</f>
+        <v>1392000</v>
+      </c>
+      <c r="H258" s="6"/>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A259" s="13"/>
+      <c r="B259" s="15" t="s">
         <v>502</v>
       </c>
-      <c r="B258" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="C258" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="D258" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="E258" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="F258" s="4">
-        <v>40</v>
-      </c>
-      <c r="G258" s="5">
-        <f t="shared" si="9"/>
-        <v>320000</v>
-      </c>
-      <c r="H258" s="2"/>
-    </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A259" s="6"/>
-      <c r="B259" s="6" t="s">
-        <v>504</v>
-      </c>
-      <c r="C259" s="6"/>
-      <c r="D259" s="6"/>
-      <c r="E259" s="6"/>
-      <c r="F259" s="7">
-        <f>SUM(F251:F258)</f>
-        <v>124</v>
-      </c>
-      <c r="G259" s="8">
-        <f>SUM(G251:G258)</f>
-        <v>992000</v>
-      </c>
-      <c r="H259" s="6"/>
-    </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A260" s="18"/>
-      <c r="B260" s="20" t="s">
-        <v>505</v>
-      </c>
-      <c r="C260" s="18"/>
-      <c r="D260" s="18"/>
-      <c r="E260" s="18"/>
-      <c r="F260" s="19">
-        <f>SUM(F65,F68,F105,F111,F119,F138,F167,F222,F248,F259)</f>
-        <v>1195</v>
-      </c>
-      <c r="G260" s="19">
-        <f>SUM(G259,G248,G222,G167,G138,G119,G111,G105,G68,G65)</f>
-        <v>9560000</v>
-      </c>
-      <c r="H260" s="18"/>
+      <c r="C259" s="13"/>
+      <c r="D259" s="13"/>
+      <c r="E259" s="13"/>
+      <c r="F259" s="14">
+        <f>SUM(F65,F68,F105,F111,F119,F138,F167,F222,F248,F258)</f>
+        <v>1245</v>
+      </c>
+      <c r="G259" s="14">
+        <f>SUM(G258,G248,G222,G167,G138,G119,G111,G105,G68,G65)</f>
+        <v>9960000</v>
+      </c>
+      <c r="H259" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A112:H112"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A120:H120"/>
+    <mergeCell ref="A168:H168"/>
     <mergeCell ref="A250:H250"/>
     <mergeCell ref="A106:H106"/>
     <mergeCell ref="A139:H139"/>
     <mergeCell ref="A223:H223"/>
     <mergeCell ref="A69:H69"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A112:H112"/>
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="A120:H120"/>
-    <mergeCell ref="A168:H168"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8358,103 +8351,103 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
-        <v>506</v>
-      </c>
-      <c r="B1" s="16"/>
+      <c r="A1" s="22" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1" s="23"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B3" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>511</v>
-      </c>
-      <c r="B6" s="17">
-        <f>開發人天評估!F260-開發人天評估!F259</f>
+        <v>508</v>
+      </c>
+      <c r="B6" s="12">
+        <f>開發人天評估!F259-開發人天評估!F258</f>
         <v>1071</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>512</v>
-      </c>
-      <c r="B7" s="17">
-        <f>開發人天評估!F259</f>
-        <v>124</v>
+        <v>509</v>
+      </c>
+      <c r="B7" s="12">
+        <f>開發人天評估!F258</f>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>513</v>
-      </c>
-      <c r="B8" s="22">
+      <c r="A8" s="16" t="s">
+        <v>510</v>
+      </c>
+      <c r="B8" s="17">
         <f>SUM(B6:B7)</f>
-        <v>1195</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
-      <c r="B9" s="17"/>
+      <c r="B9" s="12"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>514</v>
-      </c>
-      <c r="B10" s="17">
+        <v>511</v>
+      </c>
+      <c r="B10" s="12">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>515</v>
-      </c>
-      <c r="B11" s="17">
+        <v>512</v>
+      </c>
+      <c r="B11" s="12">
         <v>1000</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11"/>
-      <c r="B12" s="17"/>
+      <c r="B12" s="12"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>516</v>
-      </c>
-      <c r="B13" s="17">
+        <v>513</v>
+      </c>
+      <c r="B13" s="12">
         <f>B6*B10*B11</f>
         <v>8568000</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="B14" s="12">
+        <f>B7*B10*B11</f>
+        <v>1392000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
         <v>517</v>
       </c>
-      <c r="B14" s="17">
-        <f>B7*B10*B11</f>
-        <v>992000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
-        <v>518</v>
-      </c>
-      <c r="B15" s="22">
+      <c r="B15" s="17">
         <f>SUM(B13:B14)</f>
-        <v>9560000</v>
+        <v>9960000</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -8462,10 +8455,10 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B17" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
     </row>
   </sheetData>
